--- a/docs/jira/generated/brandycards-jira-expansion-review.xlsx
+++ b/docs/jira/generated/brandycards-jira-expansion-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd4a0da2e3c064272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Criteria" sheetId="2" r:id="Rdc41844aba634c2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="Rc0f2ed7c885f4e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xray Tests" sheetId="4" r:id="R2d8f948e4d834f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd76c570764c149e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Criteria" sheetId="2" r:id="R60d5958ad2c74c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="R5dd17ed8d3bb4d9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xray Tests" sheetId="4" r:id="R7150f1398e6a4854"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19584,8 +19584,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>400001</x:v>
@@ -19621,8 +19625,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>400002</x:v>
@@ -19658,8 +19666,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>400003</x:v>
@@ -19695,8 +19707,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>400004</x:v>
@@ -19732,8 +19748,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>400005</x:v>
@@ -19769,8 +19789,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>400006</x:v>
@@ -19806,8 +19830,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>400007</x:v>
@@ -19843,8 +19871,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>400008</x:v>
@@ -19880,8 +19912,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
         <x:v>400009</x:v>
@@ -19917,8 +19953,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>400010</x:v>
@@ -19954,8 +19994,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>400011</x:v>
@@ -19991,8 +20035,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>400012</x:v>
@@ -20028,8 +20076,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>400013</x:v>
@@ -20065,8 +20117,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>400014</x:v>
@@ -20102,8 +20158,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>400015</x:v>
@@ -20139,8 +20199,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>400016</x:v>
@@ -20176,8 +20240,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>400017</x:v>
@@ -20213,8 +20281,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>400018</x:v>
@@ -20250,8 +20322,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>400019</x:v>
@@ -20287,8 +20363,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>400020</x:v>
@@ -20324,8 +20404,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>400021</x:v>
@@ -20361,8 +20445,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>400022</x:v>
@@ -20398,8 +20486,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>400023</x:v>
@@ -20435,8 +20527,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>400024</x:v>
@@ -20472,8 +20568,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>400025</x:v>
@@ -20509,8 +20609,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>400026</x:v>
@@ -20546,8 +20650,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>400027</x:v>
@@ -20583,8 +20691,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>400028</x:v>
@@ -20620,8 +20732,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
         <x:v>400029</x:v>
@@ -20657,8 +20773,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>400030</x:v>
@@ -20694,8 +20814,12 @@
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
         <x:v>400031</x:v>
@@ -20731,8 +20855,12 @@
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
         <x:v>400032</x:v>
@@ -20768,8 +20896,12 @@
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>400033</x:v>
@@ -20805,8 +20937,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
         <x:v>400034</x:v>
@@ -20842,8 +20978,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
         <x:v>400035</x:v>
@@ -20879,8 +21019,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>400036</x:v>
@@ -20916,8 +21060,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
         <x:v>400037</x:v>
@@ -20953,8 +21101,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
         <x:v>400038</x:v>
@@ -20990,8 +21142,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
         <x:v>400039</x:v>
@@ -21027,8 +21183,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
         <x:v>400040</x:v>
@@ -21064,8 +21224,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
         <x:v>400041</x:v>
@@ -21101,8 +21265,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
         <x:v>400042</x:v>
@@ -21138,8 +21306,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
         <x:v>400043</x:v>
@@ -21175,8 +21347,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
         <x:v>400044</x:v>
@@ -21212,8 +21388,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
         <x:v>400045</x:v>
@@ -21249,8 +21429,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
         <x:v>400046</x:v>
@@ -21286,8 +21470,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
         <x:v>400047</x:v>
@@ -21323,8 +21511,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
         <x:v>400048</x:v>
@@ -21360,8 +21552,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
         <x:v>400049</x:v>
@@ -21397,8 +21593,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
         <x:v>400050</x:v>
@@ -21434,8 +21634,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D52" s="11" t="n">
         <x:v>400051</x:v>
@@ -21471,8 +21675,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D53" s="11" t="n">
         <x:v>400052</x:v>
@@ -21508,8 +21716,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
         <x:v>400053</x:v>
@@ -21545,8 +21757,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
         <x:v>400054</x:v>
@@ -21582,8 +21798,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
         <x:v>400055</x:v>
@@ -21619,8 +21839,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
         <x:v>400056</x:v>
@@ -21656,8 +21880,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
         <x:v>400057</x:v>
@@ -21693,8 +21921,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
         <x:v>400058</x:v>
@@ -21730,8 +21962,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
         <x:v>400059</x:v>
@@ -21767,8 +22003,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
         <x:v>400060</x:v>
@@ -21804,8 +22044,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
         <x:v>400061</x:v>
@@ -21841,8 +22085,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
         <x:v>400062</x:v>
@@ -21878,8 +22126,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
         <x:v>400063</x:v>
@@ -21915,8 +22167,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
         <x:v>400064</x:v>
@@ -21952,8 +22208,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
         <x:v>400065</x:v>
@@ -21989,8 +22249,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
         <x:v>400066</x:v>
@@ -22026,8 +22290,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
         <x:v>400067</x:v>
@@ -22063,8 +22331,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
         <x:v>400068</x:v>
@@ -22100,8 +22372,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
         <x:v>400069</x:v>
@@ -22137,8 +22413,12 @@
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
         <x:v>400070</x:v>
@@ -22174,8 +22454,12 @@
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
         <x:v>400071</x:v>
@@ -22211,8 +22495,12 @@
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
         <x:v>400072</x:v>
@@ -22248,8 +22536,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
         <x:v>400073</x:v>
@@ -22285,8 +22577,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
         <x:v>400074</x:v>
@@ -22322,8 +22618,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
         <x:v>400075</x:v>
@@ -22359,8 +22659,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
         <x:v>400076</x:v>
@@ -22396,8 +22700,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
         <x:v>400077</x:v>
@@ -22433,8 +22741,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
         <x:v>400078</x:v>
@@ -22470,8 +22782,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
         <x:v>400079</x:v>
@@ -22507,8 +22823,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
         <x:v>400080</x:v>
@@ -22544,8 +22864,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
         <x:v>400081</x:v>
@@ -22581,8 +22905,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
         <x:v>400082</x:v>
@@ -22618,8 +22946,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
         <x:v>400083</x:v>
@@ -22655,8 +22987,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
         <x:v>400084</x:v>
@@ -22692,8 +23028,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
         <x:v>400085</x:v>
@@ -22729,8 +23069,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
         <x:v>400086</x:v>
@@ -22766,8 +23110,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
         <x:v>400087</x:v>
@@ -22803,8 +23151,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
         <x:v>400088</x:v>
@@ -22840,8 +23192,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
         <x:v>400089</x:v>
@@ -22877,8 +23233,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
         <x:v>400090</x:v>
@@ -22914,8 +23274,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
         <x:v>400091</x:v>
@@ -22951,8 +23315,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
         <x:v>400092</x:v>
@@ -22988,8 +23356,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D94" s="11" t="n">
         <x:v>400093</x:v>
@@ -23025,8 +23397,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D95" s="11" t="n">
         <x:v>400094</x:v>
@@ -23062,8 +23438,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
         <x:v>400095</x:v>
@@ -23099,8 +23479,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
         <x:v>400096</x:v>
@@ -23136,8 +23520,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
         <x:v>400097</x:v>
@@ -23173,8 +23561,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
         <x:v>400098</x:v>
@@ -23210,8 +23602,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
         <x:v>400099</x:v>
@@ -23247,8 +23643,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
         <x:v>400100</x:v>
@@ -23284,8 +23684,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
         <x:v>400101</x:v>
@@ -23321,8 +23725,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
         <x:v>400102</x:v>
@@ -23358,8 +23766,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
         <x:v>400103</x:v>
@@ -23395,8 +23807,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
         <x:v>400104</x:v>
@@ -23432,8 +23848,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
         <x:v>400105</x:v>
@@ -23469,8 +23889,12 @@
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
         <x:v>400106</x:v>
@@ -23506,8 +23930,12 @@
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
         <x:v>400107</x:v>
@@ -23543,8 +23971,12 @@
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
         <x:v>400108</x:v>
@@ -23580,8 +24012,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
         <x:v>400109</x:v>
@@ -23617,8 +24053,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
         <x:v>400110</x:v>
@@ -23654,8 +24094,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
         <x:v>400111</x:v>
@@ -23691,8 +24135,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
         <x:v>400112</x:v>
@@ -23728,8 +24176,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D114" s="11" t="n">
         <x:v>400113</x:v>
@@ -23765,8 +24217,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D115" s="11" t="n">
         <x:v>400114</x:v>
@@ -23802,8 +24258,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D116" s="11" t="n">
         <x:v>400115</x:v>
@@ -23839,8 +24299,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D117" s="11" t="n">
         <x:v>400116</x:v>
@@ -23876,8 +24340,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D118" s="11" t="n">
         <x:v>400117</x:v>
@@ -23913,8 +24381,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D119" s="11" t="n">
         <x:v>400118</x:v>
@@ -23950,8 +24422,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D120" s="11" t="n">
         <x:v>400119</x:v>
@@ -23987,8 +24463,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D121" s="11" t="n">
         <x:v>400120</x:v>
@@ -24024,8 +24504,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D122" s="11" t="n">
         <x:v>400121</x:v>
@@ -24061,8 +24545,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D123" s="11" t="n">
         <x:v>400122</x:v>
@@ -24098,8 +24586,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D124" s="11" t="n">
         <x:v>400123</x:v>
@@ -24135,8 +24627,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D125" s="11" t="n">
         <x:v>400124</x:v>
@@ -24172,8 +24668,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D126" s="11" t="n">
         <x:v>400125</x:v>
@@ -24209,8 +24709,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D127" s="11" t="n">
         <x:v>400126</x:v>
@@ -24246,8 +24750,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D128" s="11" t="n">
         <x:v>400127</x:v>
@@ -24283,8 +24791,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D129" s="11" t="n">
         <x:v>400128</x:v>
@@ -24320,8 +24832,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D130" s="11" t="n">
         <x:v>400129</x:v>
@@ -24357,8 +24873,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D131" s="11" t="n">
         <x:v>400130</x:v>
@@ -24394,8 +24914,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D132" s="11" t="n">
         <x:v>400131</x:v>
@@ -24431,8 +24955,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D133" s="11" t="n">
         <x:v>400132</x:v>
@@ -24468,8 +24996,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D134" s="11" t="n">
         <x:v>400133</x:v>
@@ -24505,8 +25037,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D135" s="11" t="n">
         <x:v>400134</x:v>
@@ -24542,8 +25078,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D136" s="11" t="n">
         <x:v>400135</x:v>
@@ -24579,8 +25119,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D137" s="11" t="n">
         <x:v>400136</x:v>
@@ -24616,8 +25160,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D138" s="11" t="n">
         <x:v>400137</x:v>
@@ -24653,8 +25201,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D139" s="11" t="n">
         <x:v>400138</x:v>
@@ -24690,8 +25242,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D140" s="11" t="n">
         <x:v>400139</x:v>
@@ -24727,8 +25283,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D141" s="11" t="n">
         <x:v>400140</x:v>
@@ -24764,8 +25324,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D142" s="11" t="n">
         <x:v>400141</x:v>
@@ -24801,8 +25365,12 @@
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D143" s="11" t="n">
         <x:v>400142</x:v>
@@ -24838,8 +25406,12 @@
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D144" s="11" t="n">
         <x:v>400143</x:v>
@@ -24875,8 +25447,12 @@
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D145" s="11" t="n">
         <x:v>400144</x:v>
@@ -24912,8 +25488,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D146" s="11" t="n">
         <x:v>400145</x:v>
@@ -24949,8 +25529,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D147" s="11" t="n">
         <x:v>400146</x:v>
@@ -24986,8 +25570,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D148" s="11" t="n">
         <x:v>400147</x:v>
@@ -25023,8 +25611,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D149" s="11" t="n">
         <x:v>400148</x:v>
@@ -25060,8 +25652,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D150" s="11" t="n">
         <x:v>400149</x:v>
@@ -25097,8 +25693,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D151" s="11" t="n">
         <x:v>400150</x:v>
@@ -25134,8 +25734,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D152" s="11" t="n">
         <x:v>400151</x:v>
@@ -25171,8 +25775,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D153" s="11" t="n">
         <x:v>400152</x:v>
@@ -25208,8 +25816,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D154" s="11" t="n">
         <x:v>400153</x:v>
@@ -25245,8 +25857,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D155" s="11" t="n">
         <x:v>400154</x:v>
@@ -25282,8 +25898,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D156" s="11" t="n">
         <x:v>400155</x:v>
@@ -25319,8 +25939,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D157" s="11" t="n">
         <x:v>400156</x:v>
@@ -25356,8 +25980,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D158" s="11" t="n">
         <x:v>400157</x:v>
@@ -25393,8 +26021,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D159" s="11" t="n">
         <x:v>400158</x:v>
@@ -25430,8 +26062,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D160" s="11" t="n">
         <x:v>400159</x:v>
@@ -25467,8 +26103,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D161" s="11" t="n">
         <x:v>400160</x:v>
@@ -25504,8 +26144,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D162" s="11" t="n">
         <x:v>400161</x:v>
@@ -25541,8 +26185,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D163" s="11" t="n">
         <x:v>400162</x:v>
@@ -25578,8 +26226,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D164" s="11" t="n">
         <x:v>400163</x:v>
@@ -25615,8 +26267,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D165" s="11" t="n">
         <x:v>400164</x:v>
@@ -25652,8 +26308,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D166" s="11" t="n">
         <x:v>400165</x:v>
@@ -25689,8 +26349,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D167" s="11" t="n">
         <x:v>400166</x:v>
@@ -25726,8 +26390,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D168" s="11" t="n">
         <x:v>400167</x:v>
@@ -25763,8 +26431,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D169" s="11" t="n">
         <x:v>400168</x:v>
@@ -25800,8 +26472,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D170" s="11" t="n">
         <x:v>400169</x:v>
@@ -25837,8 +26513,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D171" s="11" t="n">
         <x:v>400170</x:v>
@@ -25874,8 +26554,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D172" s="11" t="n">
         <x:v>400171</x:v>
@@ -25911,8 +26595,12 @@
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D173" s="11" t="n">
         <x:v>400172</x:v>
@@ -25948,8 +26636,12 @@
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D174" s="11" t="n">
         <x:v>400173</x:v>
@@ -25985,8 +26677,12 @@
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D175" s="11" t="n">
         <x:v>400174</x:v>
@@ -26022,8 +26718,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D176" s="11" t="n">
         <x:v>400175</x:v>
@@ -26059,8 +26759,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D177" s="11" t="n">
         <x:v>400176</x:v>
@@ -26096,8 +26800,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D178" s="11" t="n">
         <x:v>400177</x:v>
@@ -26133,8 +26841,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D179" s="11" t="n">
         <x:v>400178</x:v>
@@ -26170,8 +26882,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D180" s="11" t="n">
         <x:v>400179</x:v>
@@ -26207,8 +26923,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D181" s="11" t="n">
         <x:v>400180</x:v>
@@ -26244,8 +26964,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D182" s="11" t="n">
         <x:v>400181</x:v>
@@ -26281,8 +27005,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D183" s="11" t="n">
         <x:v>400182</x:v>
@@ -26318,8 +27046,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D184" s="11" t="n">
         <x:v>400183</x:v>
@@ -26355,8 +27087,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D185" s="11" t="n">
         <x:v>400184</x:v>
@@ -26392,8 +27128,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D186" s="11" t="n">
         <x:v>400185</x:v>
@@ -26429,8 +27169,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D187" s="11" t="n">
         <x:v>400186</x:v>
@@ -26466,8 +27210,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D188" s="11" t="n">
         <x:v>400187</x:v>
@@ -26503,8 +27251,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D189" s="11" t="n">
         <x:v>400188</x:v>
@@ -26540,8 +27292,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D190" s="11" t="n">
         <x:v>400189</x:v>
@@ -26577,8 +27333,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D191" s="11" t="n">
         <x:v>400190</x:v>
@@ -26614,8 +27374,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D192" s="11" t="n">
         <x:v>400191</x:v>
@@ -26651,8 +27415,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D193" s="11" t="n">
         <x:v>400192</x:v>
@@ -26688,8 +27456,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D194" s="11" t="n">
         <x:v>400193</x:v>
@@ -26725,8 +27497,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D195" s="11" t="n">
         <x:v>400194</x:v>
@@ -26762,8 +27538,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D196" s="11" t="n">
         <x:v>400195</x:v>
@@ -26799,8 +27579,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D197" s="11" t="n">
         <x:v>400196</x:v>
@@ -26836,8 +27620,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D198" s="11" t="n">
         <x:v>400197</x:v>
@@ -26873,8 +27661,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D199" s="11" t="n">
         <x:v>400198</x:v>
@@ -26910,8 +27702,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D200" s="11" t="n">
         <x:v>400199</x:v>
@@ -26947,8 +27743,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D201" s="11" t="n">
         <x:v>400200</x:v>
@@ -26984,8 +27784,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D202" s="11" t="n">
         <x:v>400201</x:v>
@@ -27021,8 +27825,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D203" s="11" t="n">
         <x:v>400202</x:v>
@@ -27058,8 +27866,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D204" s="11" t="n">
         <x:v>400203</x:v>
@@ -27095,8 +27907,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D205" s="11" t="n">
         <x:v>400204</x:v>
@@ -27132,8 +27948,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D206" s="11" t="n">
         <x:v>400205</x:v>
@@ -27169,8 +27989,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D207" s="11" t="n">
         <x:v>400206</x:v>
@@ -27206,8 +28030,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D208" s="11" t="n">
         <x:v>400207</x:v>
@@ -27243,8 +28071,12 @@
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D209" s="11" t="n">
         <x:v>400208</x:v>
@@ -27280,8 +28112,12 @@
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D210" s="11" t="n">
         <x:v>400209</x:v>
@@ -27317,8 +28153,12 @@
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D211" s="11" t="n">
         <x:v>400210</x:v>
@@ -27354,8 +28194,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D212" s="11" t="n">
         <x:v>400211</x:v>
@@ -27391,8 +28235,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D213" s="11" t="n">
         <x:v>400212</x:v>
@@ -27428,8 +28276,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D214" s="11" t="n">
         <x:v>400213</x:v>
@@ -27465,8 +28317,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D215" s="11" t="n">
         <x:v>400214</x:v>
@@ -27502,8 +28358,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D216" s="11" t="n">
         <x:v>400215</x:v>
@@ -27539,8 +28399,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D217" s="11" t="n">
         <x:v>400216</x:v>
@@ -27576,8 +28440,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D218" s="11" t="n">
         <x:v>400217</x:v>
@@ -27613,8 +28481,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D219" s="11" t="n">
         <x:v>400218</x:v>
@@ -27650,8 +28522,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D220" s="11" t="n">
         <x:v>400219</x:v>
@@ -27687,8 +28563,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D221" s="11" t="n">
         <x:v>400220</x:v>
@@ -27724,8 +28604,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D222" s="11" t="n">
         <x:v>400221</x:v>
@@ -27761,8 +28645,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D223" s="11" t="n">
         <x:v>400222</x:v>
@@ -27798,8 +28686,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D224" s="11" t="n">
         <x:v>400223</x:v>
@@ -27835,8 +28727,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D225" s="11" t="n">
         <x:v>400224</x:v>
@@ -27872,8 +28768,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D226" s="11" t="n">
         <x:v>400225</x:v>
@@ -27909,8 +28809,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D227" s="11" t="n">
         <x:v>400226</x:v>
@@ -27946,8 +28850,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D228" s="11" t="n">
         <x:v>400227</x:v>
@@ -27983,8 +28891,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D229" s="11" t="n">
         <x:v>400228</x:v>
@@ -28020,8 +28932,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D230" s="11" t="n">
         <x:v>400229</x:v>
@@ -28057,8 +28973,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D231" s="11" t="n">
         <x:v>400230</x:v>
@@ -28094,8 +29014,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D232" s="11" t="n">
         <x:v>400231</x:v>
@@ -28131,8 +29055,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D233" s="11" t="n">
         <x:v>400232</x:v>
@@ -28168,8 +29096,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D234" s="11" t="n">
         <x:v>400233</x:v>
@@ -28205,8 +29137,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D235" s="11" t="n">
         <x:v>400234</x:v>
@@ -28242,8 +29178,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D236" s="11" t="n">
         <x:v>400235</x:v>
@@ -28279,8 +29219,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D237" s="11" t="n">
         <x:v>400236</x:v>
@@ -28316,8 +29260,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D238" s="11" t="n">
         <x:v>400237</x:v>
@@ -28353,8 +29301,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D239" s="11" t="n">
         <x:v>400238</x:v>
@@ -28390,8 +29342,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D240" s="11" t="n">
         <x:v>400239</x:v>
@@ -28427,8 +29383,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D241" s="11" t="n">
         <x:v>400240</x:v>
@@ -28464,8 +29424,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D242" s="11" t="n">
         <x:v>400241</x:v>
@@ -28501,8 +29465,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D243" s="11" t="n">
         <x:v>400242</x:v>
@@ -28538,8 +29506,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D244" s="11" t="n">
         <x:v>400243</x:v>
@@ -28575,8 +29547,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D245" s="11" t="n">
         <x:v>400244</x:v>
@@ -28612,8 +29588,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D246" s="11" t="n">
         <x:v>400245</x:v>
@@ -28649,8 +29629,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D247" s="11" t="n">
         <x:v>400246</x:v>
@@ -28686,8 +29670,12 @@
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D248" s="11" t="n">
         <x:v>400247</x:v>
@@ -28723,8 +29711,12 @@
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D249" s="11" t="n">
         <x:v>400248</x:v>
@@ -28760,8 +29752,12 @@
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D250" s="11" t="n">
         <x:v>400249</x:v>
@@ -28797,8 +29793,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D251" s="11" t="n">
         <x:v>400250</x:v>
@@ -28834,8 +29834,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D252" s="11" t="n">
         <x:v>400251</x:v>
@@ -28871,8 +29875,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D253" s="11" t="n">
         <x:v>400252</x:v>
@@ -28908,8 +29916,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D254" s="11" t="n">
         <x:v>400253</x:v>
@@ -28945,8 +29957,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D255" s="11" t="n">
         <x:v>400254</x:v>
@@ -28982,8 +29998,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D256" s="11" t="n">
         <x:v>400255</x:v>
@@ -29019,8 +30039,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D257" s="11" t="n">
         <x:v>400256</x:v>
@@ -29056,8 +30080,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D258" s="11" t="n">
         <x:v>400257</x:v>
@@ -29093,8 +30121,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D259" s="11" t="n">
         <x:v>400258</x:v>
@@ -29130,8 +30162,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D260" s="11" t="n">
         <x:v>400259</x:v>
@@ -29167,8 +30203,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D261" s="11" t="n">
         <x:v>400260</x:v>
@@ -29204,8 +30244,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D262" s="11" t="n">
         <x:v>400261</x:v>
@@ -29241,8 +30285,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D263" s="11" t="n">
         <x:v>400262</x:v>
@@ -29278,8 +30326,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D264" s="11" t="n">
         <x:v>400263</x:v>
@@ -29315,8 +30367,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D265" s="11" t="n">
         <x:v>400264</x:v>
@@ -29352,8 +30408,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D266" s="11" t="n">
         <x:v>400265</x:v>
@@ -29389,8 +30449,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D267" s="11" t="n">
         <x:v>400266</x:v>
@@ -29426,8 +30490,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D268" s="11" t="n">
         <x:v>400267</x:v>
@@ -29463,8 +30531,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D269" s="11" t="n">
         <x:v>400268</x:v>
@@ -29500,8 +30572,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D270" s="11" t="n">
         <x:v>400269</x:v>
@@ -29537,8 +30613,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D271" s="11" t="n">
         <x:v>400270</x:v>
@@ -29574,8 +30654,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D272" s="11" t="n">
         <x:v>400271</x:v>
@@ -29611,8 +30695,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D273" s="11" t="n">
         <x:v>400272</x:v>
@@ -29648,8 +30736,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D274" s="11" t="n">
         <x:v>400273</x:v>
@@ -29685,8 +30777,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D275" s="11" t="n">
         <x:v>400274</x:v>
@@ -29722,8 +30818,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D276" s="11" t="n">
         <x:v>400275</x:v>
@@ -29759,8 +30859,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D277" s="11" t="n">
         <x:v>400276</x:v>
@@ -29796,8 +30900,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D278" s="11" t="n">
         <x:v>400277</x:v>
@@ -29833,8 +30941,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D279" s="11" t="n">
         <x:v>400278</x:v>
@@ -29870,8 +30982,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D280" s="11" t="n">
         <x:v>400279</x:v>
@@ -29907,8 +31023,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D281" s="11" t="n">
         <x:v>400280</x:v>
@@ -29944,8 +31064,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D282" s="11" t="n">
         <x:v>400281</x:v>
@@ -29981,8 +31105,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D283" s="11" t="n">
         <x:v>400282</x:v>
@@ -30018,8 +31146,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D284" s="11" t="n">
         <x:v>400283</x:v>
@@ -30055,8 +31187,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D285" s="11" t="n">
         <x:v>400284</x:v>
@@ -30092,8 +31228,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D286" s="11" t="n">
         <x:v>400285</x:v>
@@ -30129,8 +31269,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D287" s="11" t="n">
         <x:v>400286</x:v>
@@ -30166,8 +31310,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D288" s="11" t="n">
         <x:v>400287</x:v>
@@ -30203,8 +31351,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D289" s="11" t="n">
         <x:v>400288</x:v>
@@ -30240,8 +31392,12 @@
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D290" s="11" t="n">
         <x:v>400289</x:v>
@@ -30277,8 +31433,12 @@
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D291" s="11" t="n">
         <x:v>400290</x:v>
@@ -30314,8 +31474,12 @@
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D292" s="11" t="n">
         <x:v>400291</x:v>
@@ -30351,8 +31515,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D293" s="11" t="n">
         <x:v>400292</x:v>
@@ -30388,8 +31556,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D294" s="11" t="n">
         <x:v>400293</x:v>
@@ -30425,8 +31597,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D295" s="11" t="n">
         <x:v>400294</x:v>
@@ -30462,8 +31638,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D296" s="11" t="n">
         <x:v>400295</x:v>
@@ -30499,8 +31679,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D297" s="11" t="n">
         <x:v>400296</x:v>
@@ -30536,8 +31720,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D298" s="11" t="n">
         <x:v>400297</x:v>
@@ -30573,8 +31761,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D299" s="11" t="n">
         <x:v>400298</x:v>
@@ -30610,8 +31802,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D300" s="11" t="n">
         <x:v>400299</x:v>
@@ -30647,8 +31843,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D301" s="11" t="n">
         <x:v>400300</x:v>
@@ -30684,8 +31884,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D302" s="11" t="n">
         <x:v>400301</x:v>
@@ -30721,8 +31925,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D303" s="11" t="n">
         <x:v>400302</x:v>
@@ -30758,8 +31966,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D304" s="11" t="n">
         <x:v>400303</x:v>
@@ -30795,8 +32007,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D305" s="11" t="n">
         <x:v>400304</x:v>
@@ -30832,8 +32048,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D306" s="11" t="n">
         <x:v>400305</x:v>
@@ -30869,8 +32089,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D307" s="11" t="n">
         <x:v>400306</x:v>
@@ -30906,8 +32130,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D308" s="11" t="n">
         <x:v>400307</x:v>
@@ -30943,8 +32171,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D309" s="11" t="n">
         <x:v>400308</x:v>
@@ -30980,8 +32212,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D310" s="11" t="n">
         <x:v>400309</x:v>
@@ -31017,8 +32253,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D311" s="11" t="n">
         <x:v>400310</x:v>
@@ -31054,8 +32294,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D312" s="11" t="n">
         <x:v>400311</x:v>
@@ -31091,8 +32335,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D313" s="11" t="n">
         <x:v>400312</x:v>
@@ -31128,8 +32376,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D314" s="11" t="n">
         <x:v>400313</x:v>
@@ -31165,8 +32417,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D315" s="11" t="n">
         <x:v>400314</x:v>
@@ -31202,8 +32458,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D316" s="11" t="n">
         <x:v>400315</x:v>
@@ -31239,8 +32499,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D317" s="11" t="n">
         <x:v>400316</x:v>
@@ -31276,8 +32540,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D318" s="11" t="n">
         <x:v>400317</x:v>
@@ -31313,8 +32581,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D319" s="11" t="n">
         <x:v>400318</x:v>
@@ -31350,8 +32622,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D320" s="11" t="n">
         <x:v>400319</x:v>
@@ -31387,8 +32663,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D321" s="11" t="n">
         <x:v>400320</x:v>
@@ -31424,8 +32704,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D322" s="11" t="n">
         <x:v>400321</x:v>
@@ -31461,8 +32745,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D323" s="11" t="n">
         <x:v>400322</x:v>
@@ -31498,8 +32786,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D324" s="11" t="n">
         <x:v>400323</x:v>
@@ -31535,8 +32827,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D325" s="11" t="n">
         <x:v>400324</x:v>
@@ -31572,8 +32868,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D326" s="11" t="n">
         <x:v>400325</x:v>
@@ -31609,8 +32909,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D327" s="11" t="n">
         <x:v>400326</x:v>
@@ -31646,8 +32950,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D328" s="11" t="n">
         <x:v>400327</x:v>
@@ -31683,8 +32991,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D329" s="11" t="n">
         <x:v>400328</x:v>
@@ -31720,8 +33032,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D330" s="11" t="n">
         <x:v>400329</x:v>
@@ -31757,8 +33073,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D331" s="11" t="n">
         <x:v>400330</x:v>
@@ -31794,8 +33114,12 @@
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D332" s="11" t="n">
         <x:v>400331</x:v>
@@ -31831,8 +33155,12 @@
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D333" s="11" t="n">
         <x:v>400332</x:v>
@@ -31868,8 +33196,12 @@
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
 Beleg und Nachbereitung
-- Ergebnis pro Schritt dokumentieren; bei Fehlern Screenshot, Request-/Correlation-ID und relevante Daten sichern.
-- Bei Fehlschlag einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.</x:v>
+- Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
+- Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
+- Alle Schritte des Tests muessen einen eigenen Nachweis besitzen; bei Eingabeschritten sind Eingabe und anschliessende Reaktion zu dokumentieren.
+- PASS nur vergeben, wenn alle Schritte erfolgreich abgeschlossen und fuer alle Schritte Screenshots hinterlegt sind.
+- FAIL oder BLOCKED ebenfalls mit Screenshot(s), tatsaechlichem Ergebnis, Datum, Tester und Umgebung dokumentieren; bei FAIL einen Bug mit Reproduktionsschritten und Verweis auf diesen Test anlegen.
+- Passwoerter, Tokens, Zahlungsdaten und sonstige Geheimnisse niemals im Klartext speichern; vor dem Anhang maskieren oder schwaerzen.</x:v>
       </x:c>
       <x:c r="D334" s="14" t="n">
         <x:v>400333</x:v>

--- a/docs/jira/generated/brandycards-jira-expansion-review.xlsx
+++ b/docs/jira/generated/brandycards-jira-expansion-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd76c570764c149e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Criteria" sheetId="2" r:id="R60d5958ad2c74c09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="R5dd17ed8d3bb4d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xray Tests" sheetId="4" r:id="R7150f1398e6a4854"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1bb3c0599d9f4ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Criteria" sheetId="2" r:id="Rf8564b8462bd426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="R74de7323fb6b46ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Xray Tests" sheetId="4" r:id="Rb1cfbd11c85c461a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19583,6 +19583,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19624,6 +19633,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19665,6 +19683,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19706,6 +19733,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19747,6 +19783,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19788,6 +19833,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19829,6 +19883,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19870,6 +19933,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19911,6 +19983,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19952,6 +20033,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -19993,6 +20083,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20034,6 +20133,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20075,6 +20183,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20116,6 +20233,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20157,6 +20283,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20198,6 +20333,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20239,6 +20383,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20280,6 +20433,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20321,6 +20483,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20362,6 +20533,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20403,6 +20583,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20444,6 +20633,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20485,6 +20683,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20526,6 +20733,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20567,6 +20783,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20608,6 +20833,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20649,6 +20883,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20690,6 +20933,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20731,6 +20983,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20772,6 +21033,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20813,6 +21083,15 @@
 4. Ergebnis erneut laden.
 Erwartetes Ergebnis
 Der Vorgang wird einmalig erfolgreich verarbeitet; alle relevanten Daten sind konsistent sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20854,6 +21133,15 @@
 4. Aktion erneut ausführen.
 Erwartetes Ergebnis
 Jeder Fehler wird am richtigen Feld erklärt; es entsteht kein halbfertiger oder doppelter Datensatz.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20895,6 +21183,15 @@
 4. Änderungsverlauf oder Log prüfen.
 Erwartetes Ergebnis
 Nicht berechtigte Zugriffe werden abgewiesen; nach einem Fehler bleibt der Zustand nachvollziehbar und wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20936,6 +21233,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -20977,6 +21283,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21018,6 +21333,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21059,6 +21383,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21100,6 +21433,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21141,6 +21483,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21182,6 +21533,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21223,6 +21583,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21264,6 +21633,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21305,6 +21683,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21346,6 +21733,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21387,6 +21783,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21428,6 +21833,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21469,6 +21883,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21510,6 +21933,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21551,6 +21983,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21592,6 +22033,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21633,6 +22083,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21674,6 +22133,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21715,6 +22183,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21756,6 +22233,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21797,6 +22283,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21838,6 +22333,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21879,6 +22383,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21920,6 +22433,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -21961,6 +22483,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22002,6 +22533,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22043,6 +22583,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22084,6 +22633,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22125,6 +22683,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22166,6 +22733,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22207,6 +22783,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22248,6 +22833,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22289,6 +22883,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22330,6 +22933,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22371,6 +22983,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22412,6 +23033,15 @@
 4. Detailansicht öffnen und zurück navigieren.
 Erwartetes Ergebnis
 Die richtigen Treffer erscheinen in stabiler Reihenfolge; der Zustand und die Produktdetails stimmen.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22453,6 +23083,15 @@
 4. Wiederholen oder Filter zurücksetzen.
 Erwartetes Ergebnis
 Leere und technische Zustände sind verständlich getrennt; die angebotenen Folgeaktionen funktionieren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22494,6 +23133,15 @@
 4. Bilder und Text bei anderer Auflösung prüfen.
 Erwartetes Ergebnis
 Kein Überlauf oder Fokusverlust tritt auf; Inhalte und Aktionen bleiben wahrnehmbar und bedienbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22535,6 +23183,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22576,6 +23233,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22617,6 +23283,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22658,6 +23333,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22699,6 +23383,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22740,6 +23433,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22781,6 +23483,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22822,6 +23533,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22863,6 +23583,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22904,6 +23633,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22945,6 +23683,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -22986,6 +23733,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23027,6 +23783,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23068,6 +23833,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23109,6 +23883,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23150,6 +23933,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23191,6 +23983,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23232,6 +24033,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23273,6 +24083,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23314,6 +24133,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23355,6 +24183,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23396,6 +24233,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23437,6 +24283,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23478,6 +24333,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23519,6 +24383,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23560,6 +24433,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23601,6 +24483,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23642,6 +24533,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23683,6 +24583,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23724,6 +24633,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23765,6 +24683,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23806,6 +24733,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23847,6 +24783,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23888,6 +24833,15 @@
 4. Zusammenfassung prüfen und Bestellung absenden.
 Erwartetes Ergebnis
 Warenkorb, Versand, Gesamtbetrag und Bestellung stimmen; der Artikel ist reserviert beziehungsweise verarbeitet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23929,6 +24883,15 @@
 4. Checkout erneut laden.
 Erwartetes Ergebnis
 Die Ursache wird verständlich angezeigt; es entsteht keine falsche Bestellung und gültige Eingaben bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -23970,6 +24933,15 @@
 4. Serverseitige Datensätze abgleichen.
 Erwartetes Ergebnis
 Es gibt genau eine fachliche Bestellung; Gast- und Kontoflow verwenden identische Preis- und Bestandsregeln.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24011,6 +24983,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24052,6 +25033,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24093,6 +25083,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24134,6 +25133,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24175,6 +25183,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24216,6 +25233,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24257,6 +25283,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24298,6 +25333,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24339,6 +25383,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24380,6 +25433,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24421,6 +25483,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24462,6 +25533,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24503,6 +25583,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24544,6 +25633,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24585,6 +25683,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24626,6 +25733,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24667,6 +25783,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24708,6 +25833,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24749,6 +25883,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24790,6 +25933,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24831,6 +25983,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24872,6 +26033,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24913,6 +26083,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24954,6 +26133,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -24995,6 +26183,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25036,6 +26233,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25077,6 +26283,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25118,6 +26333,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25159,6 +26383,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25200,6 +26433,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25241,6 +26483,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25282,6 +26533,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25323,6 +26583,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25364,6 +26633,15 @@
 4. Bestellung, Bestand und Kommunikation prüfen.
 Erwartetes Ergebnis
 Zahlbetrag, Zahlungsstatus, Bestellung und Bestand sind konsistent und genau einmal aktualisiert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25405,6 +26683,15 @@
 4. Erneuten Zahlungsversuch durchführen.
 Erwartetes Ergebnis
 Keine falsche Zahlung oder doppelte Reservierung entsteht; der Nutzer erhält eine verständliche nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25446,6 +26733,15 @@
 4. Audit und Logs prüfen.
 Erwartetes Ergebnis
 Doppelte Ereignisse haben keine Nebenwirkung; nur erlaubte Folgeaktionen werden ausgeführt und protokolliert.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25487,6 +26783,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25528,6 +26833,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25569,6 +26883,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25610,6 +26933,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25651,6 +26983,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25692,6 +27033,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25733,6 +27083,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25774,6 +27133,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25815,6 +27183,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25856,6 +27233,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25897,6 +27283,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25938,6 +27333,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -25979,6 +27383,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26020,6 +27433,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26061,6 +27483,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26102,6 +27533,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26143,6 +27583,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26184,6 +27633,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26225,6 +27683,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26266,6 +27733,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26307,6 +27783,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26348,6 +27833,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26389,6 +27883,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26430,6 +27933,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26471,6 +27983,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26512,6 +28033,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26553,6 +28083,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26594,6 +28133,15 @@
 4. Passwortreset durchführen.
 Erwartetes Ergebnis
 Nur bestätigte und korrekte Zugangsdaten erlauben Zugriff; Tokens und Fehlermeldungen verhalten sich sicher.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26635,6 +28183,15 @@
 4. Seite neu laden und erneut prüfen.
 Erwartetes Ergebnis
 Nur eigene Daten sind sichtbar; Änderungen und Bestellstatus bleiben konsistent.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26676,6 +28233,15 @@
 4. Folgezugriff und Audit kontrollieren.
 Erwartetes Ergebnis
 Fremdzugriff ist unmöglich; Datenschutzaktionen sind vollständig, bestätigt und nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26717,6 +28283,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26758,6 +28333,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26799,6 +28383,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26840,6 +28433,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26881,6 +28483,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26922,6 +28533,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -26963,6 +28583,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27004,6 +28633,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27045,6 +28683,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27086,6 +28733,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27127,6 +28783,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27168,6 +28833,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27209,6 +28883,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27250,6 +28933,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27291,6 +28983,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27332,6 +29033,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27373,6 +29083,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27414,6 +29133,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27455,6 +29183,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27496,6 +29233,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27537,6 +29283,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27578,6 +29333,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27619,6 +29383,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27660,6 +29433,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27701,6 +29483,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27742,6 +29533,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27783,6 +29583,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27824,6 +29633,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27865,6 +29683,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27906,6 +29733,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27947,6 +29783,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -27988,6 +29833,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28029,6 +29883,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28070,6 +29933,15 @@
 4. Status und Bestätigung prüfen.
 Erwartetes Ergebnis
 Das Angebot ist vollständig, eindeutig und im erwarteten Status sichtbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28111,6 +29983,15 @@
 4. Fehler beheben und erneut speichern.
 Erwartetes Ergebnis
 Fehler sind verständlich; fremde Daten bleiben geschützt; gültige Teildaten gehen nicht verloren.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28152,6 +30033,15 @@
 4. Benachrichtigungen und Audit prüfen.
 Erwartetes Ergebnis
 Jeder Übergang ist nachvollziehbar, berechtigt und erzeugt die richtigen Informationen für alle Beteiligten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28193,6 +30083,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28234,6 +30133,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28275,6 +30183,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28316,6 +30233,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28357,6 +30283,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28398,6 +30333,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28439,6 +30383,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28480,6 +30433,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28521,6 +30483,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28562,6 +30533,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28603,6 +30583,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28644,6 +30633,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28685,6 +30683,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28726,6 +30733,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28767,6 +30783,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28808,6 +30833,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28849,6 +30883,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28890,6 +30933,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28931,6 +30983,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -28972,6 +31033,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29013,6 +31083,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29054,6 +31133,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29095,6 +31183,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29136,6 +31233,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29177,6 +31283,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29218,6 +31333,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29259,6 +31383,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29300,6 +31433,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29341,6 +31483,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29382,6 +31533,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29423,6 +31583,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29464,6 +31633,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29505,6 +31683,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29546,6 +31733,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29587,6 +31783,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29628,6 +31833,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29669,6 +31883,15 @@
 4. Liste, Detail und Audit erneut laden.
 Erwartetes Ergebnis
 Die Änderung ist einmalig wirksam, sichtbar und mit verantwortlicher Rolle nachvollziehbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29710,6 +31933,15 @@
 4. Berechtigung und Audit prüfen.
 Erwartetes Ergebnis
 Unberechtigte Aktionen werden abgewiesen; kritische Aktionen benötigen bewusste Bestätigung.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29751,6 +31983,15 @@
 4. Lauf sicher wiederholen.
 Erwartetes Ergebnis
 Gültige Daten werden verarbeitet; Fehler sind isoliert, erklärbar und ohne Doppelverarbeitung wiederholbar.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29792,6 +32033,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29833,6 +32083,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29874,6 +32133,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29915,6 +32183,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29956,6 +32233,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -29997,6 +32283,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30038,6 +32333,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30079,6 +32383,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30120,6 +32433,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30161,6 +32483,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30202,6 +32533,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30243,6 +32583,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30284,6 +32633,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30325,6 +32683,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30366,6 +32733,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30407,6 +32783,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30448,6 +32833,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30489,6 +32883,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30530,6 +32933,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30571,6 +32983,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30612,6 +33033,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30653,6 +33083,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30694,6 +33133,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30735,6 +33183,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30776,6 +33233,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30817,6 +33283,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30858,6 +33333,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30899,6 +33383,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30940,6 +33433,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -30981,6 +33483,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31022,6 +33533,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31063,6 +33583,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31104,6 +33633,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31145,6 +33683,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31186,6 +33733,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31227,6 +33783,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31268,6 +33833,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31309,6 +33883,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31350,6 +33933,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31391,6 +33983,15 @@
 4. Screenshot oder Referenzabgleich erstellen.
 Erwartetes Ergebnis
 Layout, Typografie, Abstände, Bilder und primäre Aktionen entsprechen dem Designsystem ohne Überlauf.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31432,6 +34033,15 @@
 4. Erfolgreiche Aktion durchführen.
 Erwartetes Ergebnis
 Jeder Zustand ist eindeutig, verständlich und bietet die richtige nächste Aktion.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31473,6 +34083,15 @@
 4. Zoom und hohe Auflösung verwenden.
 Erwartetes Ergebnis
 Alle Kernaktionen sind erreichbar; Fokus, Kontrast, Semantik und Text-/Bildqualität bleiben erhalten.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31514,6 +34133,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31555,6 +34183,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31596,6 +34233,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31637,6 +34283,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31678,6 +34333,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31719,6 +34383,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31760,6 +34433,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31801,6 +34483,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31842,6 +34533,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31883,6 +34583,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31924,6 +34633,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -31965,6 +34683,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32006,6 +34733,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32047,6 +34783,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32088,6 +34833,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32129,6 +34883,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32170,6 +34933,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32211,6 +34983,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32252,6 +35033,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32293,6 +35083,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32334,6 +35133,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32375,6 +35183,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32416,6 +35233,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32457,6 +35283,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32498,6 +35333,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32539,6 +35383,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32580,6 +35433,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32621,6 +35483,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32662,6 +35533,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32703,6 +35583,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32744,6 +35633,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32785,6 +35683,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32826,6 +35733,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32867,6 +35783,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32908,6 +35833,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32949,6 +35883,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -32990,6 +35933,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -33031,6 +35983,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -33072,6 +36033,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -33113,6 +36083,15 @@
 4. Ergebnisse und Beleg speichern.
 Erwartetes Ergebnis
 Der Test ist ohne Rückfragen ausführbar und Ergebnis sowie Evidenz sind dem Lauf zugeordnet.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -33154,6 +36133,15 @@
 4. Coverage und Status prüfen.
 Erwartetes Ergebnis
 Die Story-Abdeckung ist sichtbar und der Teststatus fließt in Set, Plan und Release-Ansicht ein.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
@@ -33195,6 +36183,15 @@
 4. Korrektur erneut testen.
 Erwartetes Ergebnis
 Der Fehler ist reproduzierbar beschrieben; Retest und Regression aktualisieren die Abdeckung korrekt.
+Responsive Viewports
+- Desktop: 1440 x 900 CSS-Pixel.
+- Full HD: 1920 x 1080 CSS-Pixel.
+- WQHD: 2560 x 1440 CSS-Pixel.
+- Ultrawide: 3440 x 1440 CSS-Pixel.
+- 4K: 3840 x 2160 CSS-Pixel.
+- Tablet: 768 x 1024 CSS-Pixel.
+- Smartphone: 390 x 844 CSS-Pixel.
+- Bei UI-Tests jeden definierten Viewport pruefen und je Viewport einen eigenen Screenshot am Testlauf hinterlegen.
 Beleg und Nachbereitung
 - Fuer jeden einzelnen Testschritt unmittelbar nach der Ausfuehrung einen Screenshot als Anhang am Testlauf hinterlegen.
 - Der Screenshot muss die relevante Ausgangslage bzw. Eingabe und das sichtbare Ergebnis des jeweiligen Schrittes nachvollziehbar zeigen.
